--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/8443-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/8443-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E0BAF396-981F-463C-84F0-1E213A35983E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{24C53F8F-E471-41F3-B1BE-B78B8F418EAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{E1A51733-AEE2-47BB-AC1B-4F95CEAA1DDD}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{904E3152-D405-4B78-BCDE-68B5E8FEFA52}"/>
   </bookViews>
   <sheets>
     <sheet name="8443-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1451,25 +1451,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52A4B993-48B4-46F0-8FF4-1B4F6A202E10}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A269C2D3-B7AD-45D4-AF04-190391B9013D}">
   <dimension ref="A1:R27"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="9.33203125" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="7.5" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="7" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1497,7 +1497,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1527,7 +1527,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1573,7 +1573,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1623,7 +1623,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1677,7 +1677,7 @@
         <v>1.66</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1733,7 +1733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1789,7 +1789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>25</v>
       </c>
@@ -1845,7 +1845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>25</v>
       </c>
@@ -1901,7 +1901,7 @@
         <v>1.66</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="39">
         <v>2024</v>
       </c>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>25</v>
       </c>
@@ -2011,7 +2011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>25</v>
       </c>
@@ -2067,7 +2067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
         <v>25</v>
       </c>
@@ -2123,7 +2123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>25</v>
       </c>
@@ -2179,7 +2179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="37">
         <v>2023</v>
       </c>
@@ -2233,7 +2233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="39">
         <v>2022</v>
       </c>
@@ -2287,7 +2287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="37">
         <v>2021</v>
       </c>
@@ -2341,7 +2341,7 @@
         <v>1.32</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="39">
         <v>2020</v>
       </c>
@@ -2395,7 +2395,7 @@
         <v>1.47</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="37">
         <v>2019</v>
       </c>
@@ -2449,7 +2449,7 @@
         <v>3.43</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="39">
         <v>2018</v>
       </c>
@@ -2503,7 +2503,7 @@
         <v>1.99</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="37">
         <v>2017</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>1.97</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="39">
         <v>2016</v>
       </c>
@@ -2611,7 +2611,7 @@
         <v>6.65</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="37">
         <v>2015</v>
       </c>
@@ -2665,7 +2665,7 @@
         <v>6.41</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="39">
         <v>2014</v>
       </c>
@@ -2719,7 +2719,7 @@
         <v>2.87</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="37">
         <v>2013</v>
       </c>
@@ -2773,7 +2773,7 @@
         <v>6.81</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="39">
         <v>2012</v>
       </c>
@@ -2827,7 +2827,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="37" t="s">
         <v>36</v>
       </c>
